--- a/must_be_asset/must_be_subasset.xlsx
+++ b/must_be_asset/must_be_subasset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h.alavi\Documents\GitHub\RCM_data_concatinating\must_be_asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE54AE5-A7D0-4609-BB58-E97449FFFA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79AB52D-F37B-4FCB-B0B3-A4579BA3A842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>

--- a/must_be_asset/must_be_subasset.xlsx
+++ b/must_be_asset/must_be_subasset.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haddadnia\Documents\GitHub\RCM_data_concatinating\must_be_asset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h.alavi\Documents\GitHub\RCM_data_concatinating\must_be_asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84C3522-4877-49D2-AF11-999A240FD223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2527,12 +2528,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2540,7 +2541,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2548,7 +2549,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2679,21 +2680,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="C1:N231" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="C1:N231"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C1:N231" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="C1:N231" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" name="تجهیز والد"/>
-    <tableColumn id="2" name="TagNo"/>
-    <tableColumn id="3" name="نام جز"/>
-    <tableColumn id="4" name="نوع جز"/>
-    <tableColumn id="5" name="سطح تجهیز"/>
-    <tableColumn id="6" name="پارت نامبر PN"/>
-    <tableColumn id="7" name="سریال نامبر SN"/>
-    <tableColumn id="8" name="جز بالاتر (سریال نامبر بالاسری)"/>
-    <tableColumn id="9" name="مشخصه فنی"/>
-    <tableColumn id="10" name="توضیحات"/>
-    <tableColumn id="11" name="نوع فنی"/>
-    <tableColumn id="12" name="APP TagNo"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="تجهیز والد"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="TagNo"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="نام جز"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="نوع جز"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="سطح تجهیز"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="پارت نامبر PN"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="سریال نامبر SN"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="جز بالاتر (سریال نامبر بالاسری)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="مشخصه فنی"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="توضیحات"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="نوع فنی"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="APP TagNo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2775,6 +2776,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2810,6 +2828,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2985,27 +3020,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N231"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.875" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="3" max="3" width="22.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="35.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="12" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="2" customWidth="1"/>
     <col min="13" max="13" width="9" style="2"/>
-    <col min="14" max="14" width="12.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>831</v>
       </c>
@@ -3049,9 +3084,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
@@ -3075,9 +3110,9 @@
         <v>667</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -3101,7 +3136,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -3127,7 +3162,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -3153,7 +3188,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -3179,7 +3214,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -3205,7 +3240,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0</v>
       </c>
@@ -3231,7 +3266,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -3257,7 +3292,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -3288,7 +3323,7 @@
       <c r="M10"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0</v>
       </c>
@@ -3314,7 +3349,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0</v>
       </c>
@@ -3340,7 +3375,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0</v>
       </c>
@@ -3366,7 +3401,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -3397,7 +3432,7 @@
       <c r="M14"/>
       <c r="N14"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0</v>
       </c>
@@ -3423,7 +3458,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -3449,7 +3484,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -3475,7 +3510,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0</v>
       </c>
@@ -3501,7 +3536,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0</v>
       </c>
@@ -3527,7 +3562,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0</v>
       </c>
@@ -3553,7 +3588,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0</v>
       </c>
@@ -3579,7 +3614,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0</v>
       </c>
@@ -3605,7 +3640,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0</v>
       </c>
@@ -3631,7 +3666,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0</v>
       </c>
@@ -3657,7 +3692,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0</v>
       </c>
@@ -3683,7 +3718,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0</v>
       </c>
@@ -3709,7 +3744,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0</v>
       </c>
@@ -3735,7 +3770,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0</v>
       </c>
@@ -3758,7 +3793,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0</v>
       </c>
@@ -3784,7 +3819,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0</v>
       </c>
@@ -3810,7 +3845,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0</v>
       </c>
@@ -3836,7 +3871,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0</v>
       </c>
@@ -3862,7 +3897,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0</v>
       </c>
@@ -3888,7 +3923,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0</v>
       </c>
@@ -3914,7 +3949,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0</v>
       </c>
@@ -3940,7 +3975,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0</v>
       </c>
@@ -3966,7 +4001,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0</v>
       </c>
@@ -3992,7 +4027,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0</v>
       </c>
@@ -4018,7 +4053,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0</v>
       </c>
@@ -4049,7 +4084,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0</v>
       </c>
@@ -4075,7 +4110,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0</v>
       </c>
@@ -4101,7 +4136,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0</v>
       </c>
@@ -4127,7 +4162,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0</v>
       </c>
@@ -4153,7 +4188,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0</v>
       </c>
@@ -4179,7 +4214,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0</v>
       </c>
@@ -4205,7 +4240,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0</v>
       </c>
@@ -4231,7 +4266,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0</v>
       </c>
@@ -4257,7 +4292,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0</v>
       </c>
@@ -4283,7 +4318,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0</v>
       </c>
@@ -4309,7 +4344,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0</v>
       </c>
@@ -4335,7 +4370,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0</v>
       </c>
@@ -4361,7 +4396,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0</v>
       </c>
@@ -4387,7 +4422,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0</v>
       </c>
@@ -4413,7 +4448,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0</v>
       </c>
@@ -4439,7 +4474,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0</v>
       </c>
@@ -4465,7 +4500,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0</v>
       </c>
@@ -4491,7 +4526,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0</v>
       </c>
@@ -4517,7 +4552,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0</v>
       </c>
@@ -4543,7 +4578,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0</v>
       </c>
@@ -4569,7 +4604,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0</v>
       </c>
@@ -4598,7 +4633,7 @@
       <c r="M60"/>
       <c r="N60"/>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>0</v>
       </c>
@@ -4624,7 +4659,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>0</v>
       </c>
@@ -4650,7 +4685,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>0</v>
       </c>
@@ -4676,7 +4711,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>0</v>
       </c>
@@ -4702,7 +4737,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0</v>
       </c>
@@ -4728,7 +4763,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0</v>
       </c>
@@ -4754,7 +4789,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>0</v>
       </c>
@@ -4780,7 +4815,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>0</v>
       </c>
@@ -4806,7 +4841,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>0</v>
       </c>
@@ -4832,7 +4867,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0</v>
       </c>
@@ -4858,7 +4893,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>0</v>
       </c>
@@ -4884,7 +4919,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>0</v>
       </c>
@@ -4910,7 +4945,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>0</v>
       </c>
@@ -4936,7 +4971,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>0</v>
       </c>
@@ -4962,7 +4997,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>0</v>
       </c>
@@ -4988,7 +5023,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>0</v>
       </c>
@@ -5014,7 +5049,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>0</v>
       </c>
@@ -5040,7 +5075,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>0</v>
       </c>
@@ -5066,7 +5101,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>0</v>
       </c>
@@ -5097,7 +5132,7 @@
       <c r="M79"/>
       <c r="N79"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>0</v>
       </c>
@@ -5123,7 +5158,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>0</v>
       </c>
@@ -5149,7 +5184,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>0</v>
       </c>
@@ -5175,7 +5210,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>0</v>
       </c>
@@ -5201,7 +5236,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>0</v>
       </c>
@@ -5227,7 +5262,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>0</v>
       </c>
@@ -5253,7 +5288,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>0</v>
       </c>
@@ -5279,7 +5314,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>0</v>
       </c>
@@ -5305,7 +5340,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>0</v>
       </c>
@@ -5331,7 +5366,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>0</v>
       </c>
@@ -5357,7 +5392,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>0</v>
       </c>
@@ -5383,7 +5418,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>0</v>
       </c>
@@ -5409,7 +5444,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>0</v>
       </c>
@@ -5440,7 +5475,7 @@
       <c r="M92"/>
       <c r="N92"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>0</v>
       </c>
@@ -5466,7 +5501,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>0</v>
       </c>
@@ -5492,7 +5527,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>0</v>
       </c>
@@ -5523,7 +5558,7 @@
       <c r="M95"/>
       <c r="N95"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>0</v>
       </c>
@@ -5554,7 +5589,7 @@
       <c r="M96"/>
       <c r="N96"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>0</v>
       </c>
@@ -5585,7 +5620,7 @@
       <c r="M97"/>
       <c r="N97"/>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>0</v>
       </c>
@@ -5616,7 +5651,7 @@
       <c r="M98"/>
       <c r="N98"/>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>0</v>
       </c>
@@ -5647,7 +5682,7 @@
       <c r="M99"/>
       <c r="N99"/>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>0</v>
       </c>
@@ -5673,7 +5708,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>0</v>
       </c>
@@ -5699,7 +5734,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>0</v>
       </c>
@@ -5725,7 +5760,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>0</v>
       </c>
@@ -5751,7 +5786,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>0</v>
       </c>
@@ -5777,7 +5812,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>0</v>
       </c>
@@ -5803,7 +5838,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>0</v>
       </c>
@@ -5829,7 +5864,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>0</v>
       </c>
@@ -5855,7 +5890,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>0</v>
       </c>
@@ -5886,7 +5921,7 @@
       <c r="M108"/>
       <c r="N108"/>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>0</v>
       </c>
@@ -5917,7 +5952,7 @@
       <c r="M109"/>
       <c r="N109"/>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>0</v>
       </c>
@@ -5948,7 +5983,7 @@
       <c r="M110"/>
       <c r="N110"/>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>0</v>
       </c>
@@ -5979,7 +6014,7 @@
       <c r="M111"/>
       <c r="N111"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>0</v>
       </c>
@@ -6010,7 +6045,7 @@
       <c r="M112"/>
       <c r="N112"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>0</v>
       </c>
@@ -6041,7 +6076,7 @@
       <c r="M113"/>
       <c r="N113"/>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>0</v>
       </c>
@@ -6072,7 +6107,7 @@
       <c r="M114"/>
       <c r="N114"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>0</v>
       </c>
@@ -6103,7 +6138,7 @@
       <c r="M115"/>
       <c r="N115"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>0</v>
       </c>
@@ -6134,7 +6169,7 @@
       <c r="M116"/>
       <c r="N116"/>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>0</v>
       </c>
@@ -6165,7 +6200,7 @@
       <c r="M117"/>
       <c r="N117"/>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>0</v>
       </c>
@@ -6196,7 +6231,7 @@
       <c r="M118"/>
       <c r="N118"/>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>0</v>
       </c>
@@ -6227,7 +6262,7 @@
       <c r="M119"/>
       <c r="N119"/>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>0</v>
       </c>
@@ -6258,7 +6293,7 @@
       <c r="M120"/>
       <c r="N120"/>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>0</v>
       </c>
@@ -6289,7 +6324,7 @@
       <c r="M121"/>
       <c r="N121"/>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>0</v>
       </c>
@@ -6320,7 +6355,7 @@
       <c r="M122"/>
       <c r="N122"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>0</v>
       </c>
@@ -6351,7 +6386,7 @@
       <c r="M123"/>
       <c r="N123"/>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>0</v>
       </c>
@@ -6382,7 +6417,7 @@
       <c r="M124"/>
       <c r="N124"/>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>0</v>
       </c>
@@ -6408,7 +6443,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>0</v>
       </c>
@@ -6434,7 +6469,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>0</v>
       </c>
@@ -6460,7 +6495,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>0</v>
       </c>
@@ -6486,7 +6521,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>0</v>
       </c>
@@ -6512,7 +6547,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>0</v>
       </c>
@@ -6538,7 +6573,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>0</v>
       </c>
@@ -6564,7 +6599,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>0</v>
       </c>
@@ -6590,7 +6625,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>0</v>
       </c>
@@ -6616,7 +6651,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>0</v>
       </c>
@@ -6642,7 +6677,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>0</v>
       </c>
@@ -6668,7 +6703,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>0</v>
       </c>
@@ -6694,7 +6729,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>0</v>
       </c>
@@ -6720,7 +6755,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>0</v>
       </c>
@@ -6746,7 +6781,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>0</v>
       </c>
@@ -6772,7 +6807,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>0</v>
       </c>
@@ -6798,7 +6833,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>0</v>
       </c>
@@ -6824,7 +6859,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>0</v>
       </c>
@@ -6850,7 +6885,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>0</v>
       </c>
@@ -6876,7 +6911,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>0</v>
       </c>
@@ -6902,7 +6937,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>0</v>
       </c>
@@ -6928,7 +6963,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>0</v>
       </c>
@@ -6954,7 +6989,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>0</v>
       </c>
@@ -6980,7 +7015,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>0</v>
       </c>
@@ -7006,7 +7041,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>0</v>
       </c>
@@ -7032,7 +7067,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>0</v>
       </c>
@@ -7058,7 +7093,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>0</v>
       </c>
@@ -7089,7 +7124,7 @@
       <c r="M151"/>
       <c r="N151"/>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>0</v>
       </c>
@@ -7115,7 +7150,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>0</v>
       </c>
@@ -7141,7 +7176,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>0</v>
       </c>
@@ -7167,7 +7202,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>0</v>
       </c>
@@ -7193,7 +7228,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>0</v>
       </c>
@@ -7219,7 +7254,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>0</v>
       </c>
@@ -7245,7 +7280,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>0</v>
       </c>
@@ -7271,7 +7306,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>0</v>
       </c>
@@ -7297,7 +7332,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>0</v>
       </c>
@@ -7323,7 +7358,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>0</v>
       </c>
@@ -7349,7 +7384,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>0</v>
       </c>
@@ -7375,7 +7410,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>0</v>
       </c>
@@ -7401,7 +7436,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>0</v>
       </c>
@@ -7427,7 +7462,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>0</v>
       </c>
@@ -7453,7 +7488,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>0</v>
       </c>
@@ -7479,7 +7514,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>0</v>
       </c>
@@ -7505,7 +7540,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>0</v>
       </c>
@@ -7531,7 +7566,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>0</v>
       </c>
@@ -7557,7 +7592,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>0</v>
       </c>
@@ -7583,7 +7618,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>0</v>
       </c>
@@ -7609,7 +7644,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>0</v>
       </c>
@@ -7635,7 +7670,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>0</v>
       </c>
@@ -7661,7 +7696,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>0</v>
       </c>
@@ -7687,7 +7722,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>0</v>
       </c>
@@ -7713,7 +7748,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>0</v>
       </c>
@@ -7739,7 +7774,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>0</v>
       </c>
@@ -7765,7 +7800,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>0</v>
       </c>
@@ -7791,7 +7826,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>0</v>
       </c>
@@ -7817,7 +7852,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>0</v>
       </c>
@@ -7843,7 +7878,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>0</v>
       </c>
@@ -7869,7 +7904,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>0</v>
       </c>
@@ -7895,7 +7930,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>0</v>
       </c>
@@ -7921,7 +7956,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>0</v>
       </c>
@@ -7947,7 +7982,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>0</v>
       </c>
@@ -7973,7 +8008,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>0</v>
       </c>
@@ -7999,7 +8034,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>0</v>
       </c>
@@ -8025,7 +8060,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>0</v>
       </c>
@@ -8051,7 +8086,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>0</v>
       </c>
@@ -8077,7 +8112,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>0</v>
       </c>
@@ -8103,7 +8138,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>0</v>
       </c>
@@ -8129,7 +8164,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>0</v>
       </c>
@@ -8155,7 +8190,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>0</v>
       </c>
@@ -8181,7 +8216,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>0</v>
       </c>
@@ -8207,7 +8242,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>0</v>
       </c>
@@ -8233,7 +8268,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>0</v>
       </c>
@@ -8259,7 +8294,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>0</v>
       </c>
@@ -8285,7 +8320,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>0</v>
       </c>
@@ -8311,7 +8346,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>0</v>
       </c>
@@ -8337,7 +8372,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>0</v>
       </c>
@@ -8363,7 +8398,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>0</v>
       </c>
@@ -8389,7 +8424,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>0</v>
       </c>
@@ -8415,7 +8450,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>0</v>
       </c>
@@ -8441,7 +8476,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>0</v>
       </c>
@@ -8467,7 +8502,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>0</v>
       </c>
@@ -8493,7 +8528,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>0</v>
       </c>
@@ -8519,7 +8554,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>0</v>
       </c>
@@ -8545,7 +8580,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>0</v>
       </c>
@@ -8571,7 +8606,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>0</v>
       </c>
@@ -8597,7 +8632,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>0</v>
       </c>
@@ -8623,7 +8658,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>0</v>
       </c>
@@ -8649,7 +8684,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>0</v>
       </c>
@@ -8675,7 +8710,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>0</v>
       </c>
@@ -8701,7 +8736,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>0</v>
       </c>
@@ -8727,7 +8762,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>0</v>
       </c>
@@ -8753,7 +8788,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>0</v>
       </c>
@@ -8779,7 +8814,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>0</v>
       </c>
@@ -8805,7 +8840,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>0</v>
       </c>
@@ -8831,7 +8866,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>0</v>
       </c>
@@ -8862,7 +8897,7 @@
       <c r="M219"/>
       <c r="N219"/>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>0</v>
       </c>
@@ -8893,7 +8928,7 @@
       <c r="M220"/>
       <c r="N220"/>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>0</v>
       </c>
@@ -8924,7 +8959,7 @@
       <c r="M221"/>
       <c r="N221"/>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>0</v>
       </c>
@@ -8955,7 +8990,7 @@
       <c r="M222"/>
       <c r="N222"/>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>0</v>
       </c>
@@ -8986,7 +9021,7 @@
       <c r="M223"/>
       <c r="N223"/>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>0</v>
       </c>
@@ -9012,7 +9047,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>0</v>
       </c>
@@ -9038,7 +9073,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>0</v>
       </c>
@@ -9064,7 +9099,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>0</v>
       </c>
@@ -9090,7 +9125,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>0</v>
       </c>
@@ -9116,7 +9151,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>0</v>
       </c>
@@ -9142,7 +9177,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>0</v>
       </c>
@@ -9168,7 +9203,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>0</v>
       </c>

--- a/must_be_asset/must_be_subasset.xlsx
+++ b/must_be_asset/must_be_subasset.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haddadnia\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haddadnia\Documents\GitHub\RCM_data_concatinating\must_be_asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="1081">
   <si>
     <t>TagNo</t>
   </si>
@@ -3263,6 +3263,9 @@
   </si>
   <si>
     <t>0110ST01.ER521M01.UE03.BF4</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -3490,8 +3493,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table911" displayName="Table911" ref="A1:S231" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
-  <autoFilter ref="A1:S231"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table911" displayName="Table911" ref="A1:S232" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+  <autoFilter ref="A1:S232"/>
   <sortState ref="A2:P231">
     <sortCondition ref="B1:B231"/>
   </sortState>
@@ -3809,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S231"/>
+  <dimension ref="A1:S232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -14109,6 +14112,17 @@
         <v>647</v>
       </c>
     </row>
+    <row r="232" spans="1:15">
+      <c r="E232" s="6"/>
+      <c r="F232" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H232" s="6" t="str">
+        <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
+        <v/>
+      </c>
+      <c r="J232" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/must_be_asset/must_be_subasset.xlsx
+++ b/must_be_asset/must_be_subasset.xlsx
@@ -3302,7 +3302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3313,6 +3313,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3342,7 +3348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3360,6 +3366,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3493,11 +3517,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table911" displayName="Table911" ref="A1:S232" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
-  <autoFilter ref="A1:S232"/>
-  <sortState ref="A2:P231">
-    <sortCondition ref="B1:B231"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table911" displayName="Table911" ref="A1:S233" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+  <autoFilter ref="A1:S233"/>
   <tableColumns count="19">
     <tableColumn id="1" name="ردیف" dataDxfId="18"/>
     <tableColumn id="2" name="ثبت سیستم شد" dataDxfId="17"/>
@@ -3812,7 +3833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S232"/>
+  <dimension ref="A1:S233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4520,48 +4541,48 @@
         <v>631</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="2">
+    <row r="16" spans="1:19" s="10" customFormat="1">
+      <c r="A16" s="10">
         <v>16</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="10">
+        <v>0</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="2" t="str">
+      <c r="H16" s="10" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v>0120BC01</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L16" s="2">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
+      <c r="J16" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="L16" s="10">
+        <v>8</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="10" t="s">
         <v>631</v>
       </c>
     </row>
@@ -11177,48 +11198,48 @@
         <v>775</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
-      <c r="A164" s="2">
+    <row r="164" spans="1:15" s="7" customFormat="1">
+      <c r="A164" s="7">
         <v>166</v>
       </c>
-      <c r="B164" s="2">
-        <v>0</v>
-      </c>
-      <c r="C164" s="2" t="s">
+      <c r="B164" s="7">
+        <v>0</v>
+      </c>
+      <c r="C164" s="7" t="s">
         <v>944</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="D164" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="E164" s="6" t="s">
+      <c r="E164" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="F164" s="4" t="s">
+      <c r="F164" s="9" t="s">
         <v>984</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H164" s="2" t="str">
+      <c r="H164" s="7" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v>0110BF01</v>
       </c>
-      <c r="I164" s="2" t="s">
+      <c r="I164" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="J164" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L164" s="2">
-        <v>8</v>
-      </c>
-      <c r="N164" s="2" t="s">
+      <c r="J164" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="L164" s="7">
+        <v>8</v>
+      </c>
+      <c r="N164" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="O164" s="2" t="s">
+      <c r="O164" s="7" t="s">
         <v>615</v>
       </c>
     </row>
@@ -12032,138 +12053,138 @@
         <v>732</v>
       </c>
     </row>
-    <row r="183" spans="1:15">
-      <c r="A183" s="2">
+    <row r="183" spans="1:15" s="7" customFormat="1">
+      <c r="A183" s="7">
         <v>193</v>
       </c>
-      <c r="B183" s="2">
-        <v>0</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="B183" s="7">
+        <v>0</v>
+      </c>
+      <c r="C183" s="7" t="s">
         <v>963</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="D183" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E183" s="6" t="s">
+      <c r="E183" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="F183" s="9" t="s">
         <v>999</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H183" s="2" t="str">
+      <c r="H183" s="7" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v>0930BM01</v>
       </c>
-      <c r="I183" s="2" t="s">
+      <c r="I183" s="7" t="s">
         <v>1053</v>
       </c>
-      <c r="J183" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K183" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L183" s="2">
-        <v>8</v>
-      </c>
-      <c r="N183" s="2" t="s">
+      <c r="J183" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="K183" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="L183" s="7">
+        <v>8</v>
+      </c>
+      <c r="N183" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="O183" s="2" t="s">
+      <c r="O183" s="7" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="184" spans="1:15">
-      <c r="A184" s="2">
+    <row r="184" spans="1:15" s="7" customFormat="1">
+      <c r="A184" s="7">
         <v>194</v>
       </c>
-      <c r="B184" s="2">
-        <v>0</v>
-      </c>
-      <c r="C184" s="2" t="s">
+      <c r="B184" s="7">
+        <v>0</v>
+      </c>
+      <c r="C184" s="7" t="s">
         <v>964</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="D184" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E184" s="6" t="s">
+      <c r="E184" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="F184" s="4" t="s">
+      <c r="F184" s="9" t="s">
         <v>999</v>
       </c>
-      <c r="G184" s="2" t="s">
+      <c r="G184" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H184" s="2" t="str">
+      <c r="H184" s="7" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v>0930BM01</v>
       </c>
-      <c r="I184" s="2" t="s">
+      <c r="I184" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="J184" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K184" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L184" s="2">
-        <v>8</v>
-      </c>
-      <c r="N184" s="2" t="s">
+      <c r="J184" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="K184" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="L184" s="7">
+        <v>8</v>
+      </c>
+      <c r="N184" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="O184" s="2" t="s">
+      <c r="O184" s="7" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="185" spans="1:15">
-      <c r="A185" s="2">
+    <row r="185" spans="1:15" s="7" customFormat="1">
+      <c r="A185" s="7">
         <v>195</v>
       </c>
-      <c r="B185" s="2">
-        <v>0</v>
-      </c>
-      <c r="C185" s="2" t="s">
+      <c r="B185" s="7">
+        <v>0</v>
+      </c>
+      <c r="C185" s="7" t="s">
         <v>965</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D185" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="E185" s="6" t="s">
+      <c r="E185" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="F185" s="4" t="s">
+      <c r="F185" s="9" t="s">
         <v>999</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H185" s="2" t="str">
+      <c r="H185" s="7" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v>0930BM01</v>
       </c>
-      <c r="I185" s="2" t="s">
+      <c r="I185" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="J185" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K185" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L185" s="2">
-        <v>8</v>
-      </c>
-      <c r="N185" s="2" t="s">
+      <c r="J185" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="K185" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="L185" s="7">
+        <v>8</v>
+      </c>
+      <c r="N185" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="O185" s="2" t="s">
+      <c r="O185" s="7" t="s">
         <v>734</v>
       </c>
     </row>
@@ -12842,52 +12863,17 @@
         <v>716</v>
       </c>
     </row>
-    <row r="201" spans="1:15" ht="21">
-      <c r="A201" s="2">
-        <v>2</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>984</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H201" s="2" t="str">
-        <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0110BC01</v>
-      </c>
-      <c r="I201" s="2" t="s">
-        <v>156</v>
+    <row r="201" spans="1:15">
+      <c r="E201" s="6"/>
+      <c r="H201" s="6" t="str">
+        <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
+        <v/>
       </c>
       <c r="J201" s="2"/>
-      <c r="K201" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="L201" s="2">
-        <v>8</v>
-      </c>
-      <c r="N201" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O201" s="2" t="s">
-        <v>613</v>
-      </c>
     </row>
     <row r="202" spans="1:15" ht="21">
       <c r="A202" s="2">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>778</v>
@@ -12896,41 +12882,41 @@
         <v>781</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H202" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0150RL01</v>
+        <v>0110BC01</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="J202" s="2"/>
       <c r="K202" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L202" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>456</v>
+        <v>389</v>
       </c>
       <c r="O202" s="2" t="s">
-        <v>643</v>
+        <v>613</v>
       </c>
     </row>
     <row r="203" spans="1:15" ht="21">
       <c r="A203" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>778</v>
@@ -12939,7 +12925,7 @@
         <v>781</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E203" s="6" t="s">
         <v>1009</v>
@@ -12955,7 +12941,7 @@
         <v>0150RL01</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J203" s="2"/>
       <c r="K203" s="2" t="s">
@@ -12965,7 +12951,7 @@
         <v>9</v>
       </c>
       <c r="N203" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O203" s="2" t="s">
         <v>643</v>
@@ -12973,7 +12959,7 @@
     </row>
     <row r="204" spans="1:15" ht="21">
       <c r="A204" s="2">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>778</v>
@@ -12982,23 +12968,23 @@
         <v>781</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H204" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0110ST01</v>
+        <v>0150RL01</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>1061</v>
+        <v>197</v>
       </c>
       <c r="J204" s="2"/>
       <c r="K204" s="2" t="s">
@@ -13008,15 +12994,15 @@
         <v>9</v>
       </c>
       <c r="N204" s="2" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="21">
       <c r="A205" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>778</v>
@@ -13025,7 +13011,7 @@
         <v>781</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>1006</v>
@@ -13041,7 +13027,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J205" s="2"/>
       <c r="K205" s="2" t="s">
@@ -13051,7 +13037,7 @@
         <v>9</v>
       </c>
       <c r="N205" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O205" s="2" t="s">
         <v>625</v>
@@ -13059,7 +13045,7 @@
     </row>
     <row r="206" spans="1:15" ht="21">
       <c r="A206" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>778</v>
@@ -13068,7 +13054,7 @@
         <v>781</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>1006</v>
@@ -13084,7 +13070,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J206" s="2"/>
       <c r="K206" s="2" t="s">
@@ -13094,7 +13080,7 @@
         <v>9</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O206" s="2" t="s">
         <v>625</v>
@@ -13102,7 +13088,7 @@
     </row>
     <row r="207" spans="1:15" ht="21">
       <c r="A207" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>778</v>
@@ -13111,7 +13097,7 @@
         <v>781</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>1006</v>
@@ -13127,7 +13113,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="J207" s="2"/>
       <c r="K207" s="2" t="s">
@@ -13137,7 +13123,7 @@
         <v>9</v>
       </c>
       <c r="N207" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O207" s="2" t="s">
         <v>625</v>
@@ -13145,7 +13131,7 @@
     </row>
     <row r="208" spans="1:15" ht="21">
       <c r="A208" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>778</v>
@@ -13154,7 +13140,7 @@
         <v>781</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>1006</v>
@@ -13170,7 +13156,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="J208" s="2"/>
       <c r="K208" s="2" t="s">
@@ -13180,15 +13166,15 @@
         <v>9</v>
       </c>
       <c r="N208" s="2" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="O208" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="209" spans="1:15" ht="21">
       <c r="A209" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>778</v>
@@ -13213,7 +13199,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="J209" s="2"/>
       <c r="K209" s="2" t="s">
@@ -13223,7 +13209,7 @@
         <v>9</v>
       </c>
       <c r="N209" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O209" s="2" t="s">
         <v>622</v>
@@ -13231,7 +13217,7 @@
     </row>
     <row r="210" spans="1:15" ht="21">
       <c r="A210" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>778</v>
@@ -13256,7 +13242,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="J210" s="2"/>
       <c r="K210" s="2" t="s">
@@ -13266,7 +13252,7 @@
         <v>9</v>
       </c>
       <c r="N210" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="O210" s="2" t="s">
         <v>622</v>
@@ -13274,7 +13260,7 @@
     </row>
     <row r="211" spans="1:15" ht="21">
       <c r="A211" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>778</v>
@@ -13299,7 +13285,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="J211" s="2"/>
       <c r="K211" s="2" t="s">
@@ -13309,7 +13295,7 @@
         <v>9</v>
       </c>
       <c r="N211" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O211" s="2" t="s">
         <v>622</v>
@@ -13317,13 +13303,16 @@
     </row>
     <row r="212" spans="1:15" ht="21">
       <c r="A212" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>778</v>
       </c>
+      <c r="C212" s="2" t="s">
+        <v>781</v>
+      </c>
       <c r="D212" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>1006</v>
@@ -13332,171 +13321,171 @@
         <v>984</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H212" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0110BC01</v>
+        <v>0110ST01</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>154</v>
+        <v>1068</v>
       </c>
       <c r="J212" s="2"/>
       <c r="K212" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L212" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N212" s="2" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="O212" s="2" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="213" spans="1:15" ht="21">
       <c r="A213" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H213" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0130BC01</v>
+        <v>0110BC01</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J213" s="2"/>
       <c r="K213" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L213" s="2">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="N213" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="O213" s="2" t="s">
-        <v>638</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="1:15" ht="21">
       <c r="A214" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="H214" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0710TG01</v>
+        <v>0130BC01</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="J214" s="2"/>
       <c r="K214" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L214" s="2">
-        <v>6</v>
-      </c>
-      <c r="N214" s="2" t="s">
-        <v>536</v>
+        <v>8</v>
       </c>
       <c r="O214" s="2" t="s">
-        <v>710</v>
+        <v>638</v>
       </c>
     </row>
     <row r="215" spans="1:15" ht="21">
       <c r="A215" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="H215" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0930IM01</v>
+        <v>0710TG01</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>1069</v>
+        <v>266</v>
       </c>
       <c r="J215" s="2"/>
       <c r="K215" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L215" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N215" s="2" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="O215" s="2" t="s">
-        <v>733</v>
+        <v>710</v>
       </c>
     </row>
     <row r="216" spans="1:15" ht="21">
       <c r="A216" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="H216" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0150RL01</v>
+        <v>0930IM01</v>
       </c>
       <c r="I216" s="2" t="s">
-        <v>198</v>
+        <v>1069</v>
       </c>
       <c r="J216" s="2"/>
       <c r="K216" s="2" t="s">
@@ -13506,21 +13495,21 @@
         <v>9</v>
       </c>
       <c r="N216" s="2" t="s">
-        <v>458</v>
+        <v>567</v>
       </c>
       <c r="O216" s="2" t="s">
-        <v>644</v>
+        <v>733</v>
       </c>
     </row>
     <row r="217" spans="1:15" ht="21">
       <c r="A217" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E217" s="6" t="s">
         <v>1009</v>
@@ -13536,7 +13525,7 @@
         <v>0150RL01</v>
       </c>
       <c r="I217" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J217" s="2"/>
       <c r="K217" s="2" t="s">
@@ -13546,21 +13535,21 @@
         <v>9</v>
       </c>
       <c r="N217" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O217" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="21">
       <c r="A218" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>1009</v>
@@ -13576,7 +13565,7 @@
         <v>0150RL01</v>
       </c>
       <c r="I218" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J218" s="2"/>
       <c r="K218" s="2" t="s">
@@ -13586,7 +13575,7 @@
         <v>9</v>
       </c>
       <c r="N218" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O218" s="2" t="s">
         <v>645</v>
@@ -13594,13 +13583,13 @@
     </row>
     <row r="219" spans="1:15" ht="21">
       <c r="A219" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>1009</v>
@@ -13616,7 +13605,7 @@
         <v>0150RL01</v>
       </c>
       <c r="I219" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J219" s="2"/>
       <c r="K219" s="2" t="s">
@@ -13626,77 +13615,77 @@
         <v>9</v>
       </c>
       <c r="N219" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O219" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:15" ht="21">
       <c r="A220" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="H220" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0730AN01</v>
+        <v>0150RL01</v>
       </c>
       <c r="I220" s="2" t="s">
-        <v>1070</v>
+        <v>201</v>
       </c>
       <c r="J220" s="2"/>
       <c r="K220" s="2" t="s">
         <v>387</v>
       </c>
       <c r="L220" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>537</v>
+        <v>461</v>
       </c>
       <c r="O220" s="2" t="s">
-        <v>711</v>
+        <v>646</v>
       </c>
     </row>
     <row r="221" spans="1:15" ht="21">
       <c r="A221" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="H221" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>ER311M01</v>
+        <v>0730AN01</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>174</v>
+        <v>1070</v>
       </c>
       <c r="J221" s="2"/>
       <c r="K221" s="2" t="s">
@@ -13706,37 +13695,37 @@
         <v>8</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="O221" s="2" t="s">
-        <v>630</v>
+        <v>711</v>
       </c>
     </row>
     <row r="222" spans="1:15" ht="21">
       <c r="A222" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>1006</v>
+        <v>1025</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H222" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>0110ST01</v>
+        <v>ER311M01</v>
       </c>
       <c r="I222" s="2" t="s">
-        <v>1071</v>
+        <v>174</v>
       </c>
       <c r="J222" s="2"/>
       <c r="K222" s="2" t="s">
@@ -13746,21 +13735,21 @@
         <v>8</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="O222" s="2" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="223" spans="1:15" ht="21">
       <c r="A223" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>1006</v>
@@ -13776,7 +13765,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I223" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="J223" s="2"/>
       <c r="K223" s="2" t="s">
@@ -13786,7 +13775,7 @@
         <v>8</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O223" s="2" t="s">
         <v>620</v>
@@ -13794,13 +13783,13 @@
     </row>
     <row r="224" spans="1:15" ht="21">
       <c r="A224" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>1006</v>
@@ -13816,7 +13805,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="J224" s="2"/>
       <c r="K224" s="2" t="s">
@@ -13826,7 +13815,7 @@
         <v>8</v>
       </c>
       <c r="N224" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O224" s="2" t="s">
         <v>620</v>
@@ -13834,13 +13823,13 @@
     </row>
     <row r="225" spans="1:15" ht="21">
       <c r="A225" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>1006</v>
@@ -13856,7 +13845,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I225" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="J225" s="2"/>
       <c r="K225" s="2" t="s">
@@ -13866,7 +13855,7 @@
         <v>8</v>
       </c>
       <c r="N225" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O225" s="2" t="s">
         <v>620</v>
@@ -13874,13 +13863,13 @@
     </row>
     <row r="226" spans="1:15" ht="21">
       <c r="A226" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>1006</v>
@@ -13896,7 +13885,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I226" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="J226" s="2"/>
       <c r="K226" s="2" t="s">
@@ -13906,7 +13895,7 @@
         <v>8</v>
       </c>
       <c r="N226" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O226" s="2" t="s">
         <v>620</v>
@@ -13914,13 +13903,13 @@
     </row>
     <row r="227" spans="1:15" ht="21">
       <c r="A227" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>1006</v>
@@ -13936,7 +13925,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I227" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="J227" s="2"/>
       <c r="K227" s="2" t="s">
@@ -13946,7 +13935,7 @@
         <v>8</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O227" s="2" t="s">
         <v>620</v>
@@ -13954,13 +13943,13 @@
     </row>
     <row r="228" spans="1:15" ht="21">
       <c r="A228" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>1006</v>
@@ -13976,7 +13965,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="J228" s="2"/>
       <c r="K228" s="2" t="s">
@@ -13986,7 +13975,7 @@
         <v>8</v>
       </c>
       <c r="N228" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="O228" s="2" t="s">
         <v>620</v>
@@ -13994,13 +13983,13 @@
     </row>
     <row r="229" spans="1:15" ht="21">
       <c r="A229" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>1006</v>
@@ -14016,7 +14005,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="J229" s="2"/>
       <c r="K229" s="2" t="s">
@@ -14026,7 +14015,7 @@
         <v>8</v>
       </c>
       <c r="N229" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="O229" s="2" t="s">
         <v>620</v>
@@ -14034,13 +14023,13 @@
     </row>
     <row r="230" spans="1:15" ht="21">
       <c r="A230" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>1006</v>
@@ -14056,7 +14045,7 @@
         <v>0110ST01</v>
       </c>
       <c r="I230" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="J230" s="2"/>
       <c r="K230" s="2" t="s">
@@ -14066,7 +14055,7 @@
         <v>8</v>
       </c>
       <c r="N230" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O230" s="2" t="s">
         <v>620</v>
@@ -14074,29 +14063,29 @@
     </row>
     <row r="231" spans="1:15" ht="21">
       <c r="A231" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>778</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H231" s="2" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
-        <v>ER041M01</v>
+        <v>0110ST01</v>
       </c>
       <c r="I231" s="2" t="s">
-        <v>202</v>
+        <v>1079</v>
       </c>
       <c r="J231" s="2"/>
       <c r="K231" s="2" t="s">
@@ -14106,22 +14095,62 @@
         <v>8</v>
       </c>
       <c r="N231" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="O231" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" ht="21">
+      <c r="A232" s="2">
+        <v>225</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H232" s="2" t="str">
+        <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
+        <v>ER041M01</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J232" s="2"/>
+      <c r="K232" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L232" s="2">
+        <v>8</v>
+      </c>
+      <c r="N232" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="O231" s="2" t="s">
+      <c r="O232" s="2" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
-      <c r="E232" s="6"/>
-      <c r="F232" s="4" t="s">
+    <row r="233" spans="1:15">
+      <c r="E233" s="6"/>
+      <c r="F233" s="4" t="s">
         <v>1080</v>
       </c>
-      <c r="H232" s="6" t="str">
+      <c r="H233" s="6" t="str">
         <f>MID(Table911[[#This Row],[TagNo]],1,8)</f>
         <v/>
       </c>
-      <c r="J232" s="2"/>
+      <c r="J233" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/must_be_asset/must_be_subasset.xlsx
+++ b/must_be_asset/must_be_subasset.xlsx
@@ -3916,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>782</v>
@@ -3961,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>783</v>
@@ -4006,7 +4006,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>784</v>
@@ -4051,7 +4051,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>785</v>
@@ -4096,7 +4096,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>786</v>
@@ -4141,7 +4141,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>787</v>
@@ -4186,7 +4186,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>788</v>
@@ -4231,7 +4231,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>789</v>
@@ -4276,7 +4276,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>790</v>
@@ -4321,7 +4321,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>791</v>
@@ -4366,7 +4366,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>792</v>
@@ -4411,7 +4411,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>793</v>
@@ -4456,7 +4456,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>794</v>
@@ -4501,7 +4501,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>795</v>
@@ -4545,8 +4545,8 @@
       <c r="A16" s="10">
         <v>16</v>
       </c>
-      <c r="B16" s="10">
-        <v>0</v>
+      <c r="B16" s="2">
+        <v>1</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>796</v>
@@ -4591,7 +4591,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>797</v>
@@ -4636,7 +4636,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>798</v>
@@ -4681,7 +4681,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>799</v>
@@ -4726,7 +4726,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>800</v>
@@ -4771,7 +4771,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>801</v>
@@ -4816,7 +4816,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>802</v>
@@ -4861,7 +4861,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>803</v>
@@ -4906,7 +4906,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>804</v>
@@ -4951,7 +4951,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>805</v>
@@ -4993,7 +4993,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>806</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>807</v>
@@ -5083,7 +5083,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>808</v>
@@ -5128,7 +5128,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>809</v>
@@ -5173,7 +5173,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>810</v>
@@ -5218,7 +5218,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>811</v>
@@ -5263,7 +5263,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>812</v>
@@ -5308,7 +5308,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>813</v>
@@ -5353,7 +5353,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>814</v>
@@ -5398,7 +5398,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>815</v>
@@ -5443,7 +5443,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>816</v>
@@ -5488,7 +5488,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>817</v>
@@ -5533,7 +5533,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>818</v>
@@ -5578,7 +5578,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>819</v>
@@ -5623,7 +5623,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>820</v>
@@ -5668,7 +5668,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>821</v>
@@ -5713,7 +5713,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>822</v>
@@ -5758,7 +5758,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>823</v>
@@ -5803,7 +5803,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>824</v>
@@ -5848,7 +5848,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>825</v>
@@ -5893,7 +5893,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>826</v>
@@ -5938,7 +5938,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>827</v>
@@ -5983,7 +5983,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>828</v>
@@ -6028,7 +6028,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>829</v>
@@ -6073,7 +6073,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>830</v>
@@ -6118,7 +6118,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>831</v>
@@ -6163,7 +6163,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>832</v>
@@ -6208,7 +6208,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>833</v>
@@ -6253,7 +6253,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>834</v>
@@ -6298,7 +6298,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>835</v>
@@ -6343,7 +6343,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>836</v>
@@ -6388,7 +6388,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>837</v>
@@ -6433,7 +6433,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>838</v>
@@ -6478,7 +6478,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>839</v>
@@ -6523,7 +6523,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>840</v>
@@ -6568,7 +6568,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>841</v>
@@ -6613,7 +6613,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>842</v>
@@ -6658,7 +6658,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>843</v>
@@ -6703,7 +6703,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>844</v>
@@ -6748,7 +6748,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>845</v>
@@ -6793,7 +6793,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>846</v>
@@ -6838,7 +6838,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>847</v>
@@ -6883,7 +6883,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>848</v>
@@ -6928,7 +6928,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>849</v>
@@ -6973,7 +6973,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>850</v>
@@ -7018,7 +7018,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>851</v>
@@ -7063,7 +7063,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>852</v>
@@ -7108,7 +7108,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>853</v>
@@ -7153,7 +7153,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>854</v>
@@ -7198,7 +7198,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>855</v>
@@ -7243,7 +7243,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>856</v>
@@ -7288,7 +7288,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>857</v>
@@ -7333,7 +7333,7 @@
         <v>80</v>
       </c>
       <c r="B78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>858</v>
@@ -7378,7 +7378,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>859</v>
@@ -7423,7 +7423,7 @@
         <v>82</v>
       </c>
       <c r="B80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>860</v>
@@ -7468,7 +7468,7 @@
         <v>83</v>
       </c>
       <c r="B81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>861</v>
@@ -7513,7 +7513,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>862</v>
@@ -7558,7 +7558,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>863</v>
@@ -7603,7 +7603,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>864</v>
@@ -7648,7 +7648,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>865</v>
@@ -7693,7 +7693,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>866</v>
@@ -7738,7 +7738,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>867</v>
@@ -7783,7 +7783,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>868</v>
@@ -7828,7 +7828,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>869</v>
@@ -7873,7 +7873,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>870</v>
@@ -7918,7 +7918,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>871</v>
@@ -7963,7 +7963,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>872</v>
@@ -8008,7 +8008,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>873</v>
@@ -8053,7 +8053,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>874</v>
@@ -8098,7 +8098,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>875</v>
@@ -8143,7 +8143,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>876</v>
@@ -8188,7 +8188,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>877</v>
@@ -8233,7 +8233,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>878</v>
@@ -8278,7 +8278,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>879</v>
@@ -8323,7 +8323,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>880</v>
@@ -8368,7 +8368,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>881</v>
@@ -8413,7 +8413,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>882</v>
@@ -8458,7 +8458,7 @@
         <v>105</v>
       </c>
       <c r="B103" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>883</v>
@@ -8503,7 +8503,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>884</v>
@@ -8548,7 +8548,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>885</v>
@@ -8593,7 +8593,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>886</v>
@@ -8638,7 +8638,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>887</v>
@@ -8683,7 +8683,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>888</v>
@@ -8728,7 +8728,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>889</v>
@@ -8773,7 +8773,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>890</v>
@@ -8818,7 +8818,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>891</v>
@@ -8863,7 +8863,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>892</v>
@@ -8908,7 +8908,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>893</v>
@@ -8953,7 +8953,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>894</v>
@@ -8998,7 +8998,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>895</v>
@@ -9043,7 +9043,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>896</v>
@@ -9088,7 +9088,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>897</v>
@@ -9133,7 +9133,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>898</v>
@@ -9178,7 +9178,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>899</v>
@@ -9223,7 +9223,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>900</v>
@@ -9268,7 +9268,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>901</v>
@@ -9313,7 +9313,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>902</v>
@@ -9358,7 +9358,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>903</v>
@@ -9403,7 +9403,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>904</v>
@@ -9448,7 +9448,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>905</v>
@@ -9493,7 +9493,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>906</v>
@@ -9538,7 +9538,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>907</v>
@@ -9583,7 +9583,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>908</v>
@@ -9628,7 +9628,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>909</v>
@@ -9673,7 +9673,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>910</v>
@@ -9718,7 +9718,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>911</v>
@@ -9763,7 +9763,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>912</v>
@@ -9808,7 +9808,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>913</v>
@@ -9853,7 +9853,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>914</v>
@@ -9898,7 +9898,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>915</v>
@@ -9943,7 +9943,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>916</v>
@@ -9988,7 +9988,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>917</v>
@@ -10033,7 +10033,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>918</v>
@@ -10078,7 +10078,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>919</v>
@@ -10123,7 +10123,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>920</v>
@@ -10168,7 +10168,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>921</v>
@@ -10213,7 +10213,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>922</v>
@@ -10258,7 +10258,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>923</v>
@@ -10303,7 +10303,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>924</v>
@@ -10348,7 +10348,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>925</v>
@@ -10393,7 +10393,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>926</v>
@@ -10438,7 +10438,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>927</v>
@@ -10483,7 +10483,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>928</v>
@@ -10528,7 +10528,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>929</v>
@@ -10573,7 +10573,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>930</v>
@@ -10618,7 +10618,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>931</v>
@@ -10663,7 +10663,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>932</v>
@@ -10708,7 +10708,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>933</v>
@@ -10753,7 +10753,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>934</v>
@@ -10798,7 +10798,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>935</v>
@@ -10843,7 +10843,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>936</v>
@@ -10888,7 +10888,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>937</v>
@@ -10933,7 +10933,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>938</v>
@@ -10978,7 +10978,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>939</v>
@@ -11023,7 +11023,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>940</v>
@@ -11068,7 +11068,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>941</v>
@@ -11113,7 +11113,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>942</v>
@@ -11158,7 +11158,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>943</v>
@@ -11248,7 +11248,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>945</v>
@@ -11293,7 +11293,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>946</v>
@@ -11338,7 +11338,7 @@
         <v>173</v>
       </c>
       <c r="B167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>947</v>
@@ -11383,7 +11383,7 @@
         <v>174</v>
       </c>
       <c r="B168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>948</v>
@@ -11428,7 +11428,7 @@
         <v>175</v>
       </c>
       <c r="B169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>949</v>
@@ -11473,7 +11473,7 @@
         <v>176</v>
       </c>
       <c r="B170" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>950</v>
@@ -11518,7 +11518,7 @@
         <v>177</v>
       </c>
       <c r="B171" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>951</v>
@@ -11563,7 +11563,7 @@
         <v>178</v>
       </c>
       <c r="B172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>952</v>
@@ -11608,7 +11608,7 @@
         <v>183</v>
       </c>
       <c r="B173" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>953</v>
@@ -11653,7 +11653,7 @@
         <v>184</v>
       </c>
       <c r="B174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>954</v>
@@ -11698,7 +11698,7 @@
         <v>185</v>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>955</v>
@@ -11743,7 +11743,7 @@
         <v>186</v>
       </c>
       <c r="B176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>956</v>
@@ -11788,7 +11788,7 @@
         <v>187</v>
       </c>
       <c r="B177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>957</v>
@@ -11833,7 +11833,7 @@
         <v>188</v>
       </c>
       <c r="B178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>958</v>
@@ -11878,7 +11878,7 @@
         <v>189</v>
       </c>
       <c r="B179" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>959</v>
@@ -11923,7 +11923,7 @@
         <v>190</v>
       </c>
       <c r="B180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>960</v>
@@ -11968,7 +11968,7 @@
         <v>191</v>
       </c>
       <c r="B181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>961</v>
@@ -12013,7 +12013,7 @@
         <v>192</v>
       </c>
       <c r="B182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>962</v>
@@ -12193,7 +12193,7 @@
         <v>196</v>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>966</v>
@@ -12238,7 +12238,7 @@
         <v>197</v>
       </c>
       <c r="B187" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>967</v>
@@ -12283,7 +12283,7 @@
         <v>198</v>
       </c>
       <c r="B188" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>968</v>
@@ -12328,7 +12328,7 @@
         <v>208</v>
       </c>
       <c r="B189" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>969</v>
@@ -12373,7 +12373,7 @@
         <v>209</v>
       </c>
       <c r="B190" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>970</v>
@@ -12418,7 +12418,7 @@
         <v>210</v>
       </c>
       <c r="B191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>971</v>
@@ -12463,7 +12463,7 @@
         <v>211</v>
       </c>
       <c r="B192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>972</v>
@@ -12508,7 +12508,7 @@
         <v>212</v>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>973</v>
@@ -12553,7 +12553,7 @@
         <v>214</v>
       </c>
       <c r="B194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>974</v>
@@ -12598,7 +12598,7 @@
         <v>215</v>
       </c>
       <c r="B195" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>975</v>
@@ -12643,7 +12643,7 @@
         <v>226</v>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>976</v>
@@ -12688,7 +12688,7 @@
         <v>227</v>
       </c>
       <c r="B197" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>977</v>
@@ -12733,7 +12733,7 @@
         <v>228</v>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>978</v>
@@ -12778,7 +12778,7 @@
         <v>229</v>
       </c>
       <c r="B199" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>979</v>
@@ -12823,7 +12823,7 @@
         <v>230</v>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>980</v>
